--- a/artfynd/A 44207-2025 artfynd.xlsx
+++ b/artfynd/A 44207-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128842818</v>
       </c>
       <c r="B2" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128842753</v>
       </c>
       <c r="B3" t="n">
-        <v>79148</v>
+        <v>79152</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44207-2025 artfynd.xlsx
+++ b/artfynd/A 44207-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128842818</v>
       </c>
       <c r="B2" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128842753</v>
       </c>
       <c r="B3" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44207-2025 artfynd.xlsx
+++ b/artfynd/A 44207-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128842818</v>
       </c>
       <c r="B2" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128842753</v>
       </c>
       <c r="B3" t="n">
-        <v>79156</v>
+        <v>79061</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44207-2025 artfynd.xlsx
+++ b/artfynd/A 44207-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>129072873</v>
       </c>
       <c r="B5" t="n">
-        <v>92095</v>
+        <v>92100</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44207-2025 artfynd.xlsx
+++ b/artfynd/A 44207-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128842818</v>
       </c>
       <c r="B2" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128842753</v>
       </c>
       <c r="B3" t="n">
-        <v>79066</v>
+        <v>79067</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129072539</v>
       </c>
       <c r="B4" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129072873</v>
       </c>
       <c r="B5" t="n">
-        <v>92100</v>
+        <v>92103</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44207-2025 artfynd.xlsx
+++ b/artfynd/A 44207-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128842818</v>
       </c>
       <c r="B2" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128842753</v>
       </c>
       <c r="B3" t="n">
-        <v>79067</v>
+        <v>79071</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129072539</v>
       </c>
       <c r="B4" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129072873</v>
       </c>
       <c r="B5" t="n">
-        <v>92103</v>
+        <v>92110</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44207-2025 artfynd.xlsx
+++ b/artfynd/A 44207-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>129072873</v>
       </c>
       <c r="B5" t="n">
-        <v>92110</v>
+        <v>92117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44207-2025 artfynd.xlsx
+++ b/artfynd/A 44207-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128842818</v>
       </c>
       <c r="B2" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128842753</v>
       </c>
       <c r="B3" t="n">
-        <v>79071</v>
+        <v>79073</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129072539</v>
       </c>
       <c r="B4" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129072873</v>
       </c>
       <c r="B5" t="n">
-        <v>92117</v>
+        <v>92119</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44207-2025 artfynd.xlsx
+++ b/artfynd/A 44207-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>129072873</v>
       </c>
       <c r="B5" t="n">
-        <v>92119</v>
+        <v>92134</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44207-2025 artfynd.xlsx
+++ b/artfynd/A 44207-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>129072873</v>
       </c>
       <c r="B5" t="n">
-        <v>92134</v>
+        <v>92135</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44207-2025 artfynd.xlsx
+++ b/artfynd/A 44207-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128842818</v>
       </c>
       <c r="B2" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128842753</v>
       </c>
       <c r="B3" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129072539</v>
       </c>
       <c r="B4" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129072873</v>
       </c>
       <c r="B5" t="n">
-        <v>92135</v>
+        <v>92138</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44207-2025 artfynd.xlsx
+++ b/artfynd/A 44207-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>129072539</v>
       </c>
       <c r="B4" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129072873</v>
       </c>
       <c r="B5" t="n">
-        <v>92138</v>
+        <v>92140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44207-2025 artfynd.xlsx
+++ b/artfynd/A 44207-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>129072873</v>
       </c>
       <c r="B5" t="n">
-        <v>92140</v>
+        <v>92144</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44207-2025 artfynd.xlsx
+++ b/artfynd/A 44207-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>129072873</v>
       </c>
       <c r="B5" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44207-2025 artfynd.xlsx
+++ b/artfynd/A 44207-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>129072873</v>
       </c>
       <c r="B5" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44207-2025 artfynd.xlsx
+++ b/artfynd/A 44207-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128842818</v>
+        <v>128842753</v>
       </c>
       <c r="B2" t="n">
-        <v>80148</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476830</v>
+        <v>476855</v>
       </c>
       <c r="R2" t="n">
-        <v>6851146</v>
+        <v>6851118</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128842753</v>
+        <v>129072873</v>
       </c>
       <c r="B3" t="n">
-        <v>79075</v>
+        <v>92509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476855</v>
+        <v>476833</v>
       </c>
       <c r="R3" t="n">
-        <v>6851118</v>
+        <v>6851157</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -857,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129072539</v>
+        <v>128842818</v>
       </c>
       <c r="B4" t="n">
-        <v>80149</v>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476837</v>
+        <v>476830</v>
       </c>
       <c r="R4" t="n">
-        <v>6851144</v>
+        <v>6851146</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -934,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -954,44 +954,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129072873</v>
+        <v>129072539</v>
       </c>
       <c r="B5" t="n">
-        <v>92148</v>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476833</v>
+        <v>476837</v>
       </c>
       <c r="R5" t="n">
-        <v>6851157</v>
+        <v>6851144</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1060,6 +1060,112 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121149886</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>476757</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6851107</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44207-2025 artfynd.xlsx
+++ b/artfynd/A 44207-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128842753</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129072873</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128842818</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129072539</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1166,8 +1191,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149886</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 44207-2025 artfynd.xlsx
+++ b/artfynd/A 44207-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1088,49 +1088,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121149886</v>
+        <v>135914043</v>
       </c>
       <c r="B6" t="n">
-        <v>97989</v>
+        <v>99276</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fågelsjö, Dlr</t>
+          <t>Blästermyran, Blästermyran, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476757</v>
+        <v>476815</v>
       </c>
       <c r="R6" t="n">
-        <v>6851107</v>
+        <v>6851087</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1157,17 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1182,16 +1173,127 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135914043</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121149886</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Fågelsjö, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>476757</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6851107</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/121149886</t>
         </is>
@@ -1204,6 +1306,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
